--- a/docs/01_db/テーブル定義書.xlsx
+++ b/docs/01_db/テーブル定義書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\fullness\cs-training\Web_App_Exercise\docs\01_db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31C28060-8CD3-41E7-AD34-52D15F766B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ED86CB3-F985-4B4F-9634-5E75774FCE99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{0220337B-882E-4B34-BA5B-4589BE8C5B76}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0220337B-882E-4B34-BA5B-4589BE8C5B76}"/>
   </bookViews>
   <sheets>
     <sheet name="部署テーブル" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="47">
   <si>
     <t>システム名</t>
     <rPh sb="4" eb="5">
@@ -182,20 +182,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>社員名</t>
-    <rPh sb="0" eb="2">
-      <t>シャイン</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>メイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>emp_age</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>integer</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -220,16 +206,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>社員の年齢</t>
-    <rPh sb="0" eb="2">
-      <t>シャイン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ネンレイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>外部キー</t>
     <rPh sb="0" eb="2">
       <t>ガイブ</t>
@@ -281,6 +257,54 @@
     <t>ユーザー名</t>
     <rPh sb="4" eb="5">
       <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UNIQUE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>birthday</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>date</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mail_address</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>varchar(50)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社員名</t>
+    <rPh sb="0" eb="3">
+      <t>シャインメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>説明</t>
+    <rPh sb="0" eb="2">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メールアドレス(一意)</t>
+    <rPh sb="8" eb="10">
+      <t>イチイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>生年月日</t>
+    <rPh sb="0" eb="4">
+      <t>セイネンガッピ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -395,7 +419,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -440,6 +464,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -775,7 +802,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A77A606-E3D2-44C1-BA6B-29CFA522C856}">
-  <dimension ref="B2:M6"/>
+  <dimension ref="B2:N6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="12.6640625" customWidth="1"/>
@@ -784,11 +811,11 @@
     <col min="7" max="7" width="7.08203125" customWidth="1"/>
     <col min="8" max="9" width="12.6640625" customWidth="1"/>
     <col min="10" max="10" width="8.6640625" customWidth="1"/>
-    <col min="12" max="12" width="12.6640625" customWidth="1"/>
-    <col min="13" max="13" width="41" customWidth="1"/>
+    <col min="12" max="13" width="12.6640625" customWidth="1"/>
+    <col min="14" max="14" width="41" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -806,7 +833,7 @@
       </c>
       <c r="H2" s="14"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="5" t="s">
         <v>3</v>
       </c>
@@ -829,19 +856,22 @@
         <v>12</v>
       </c>
       <c r="J3" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" s="7" t="s">
         <v>28</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>31</v>
       </c>
       <c r="L3" s="7" t="s">
         <v>13</v>
       </c>
       <c r="M3" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="N3" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="8" t="s">
         <v>7</v>
       </c>
@@ -857,18 +887,21 @@
       <c r="I4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K4" s="6"/>
-      <c r="L4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="M4" s="3" t="s">
+      <c r="J4" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="M4" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="N4" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="11" t="s">
         <v>8</v>
       </c>
@@ -884,16 +917,19 @@
       <c r="I5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="M5" s="3" t="s">
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="N5" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="6" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B4:E4"/>
@@ -907,7 +943,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{142469DF-ECD7-41EE-A139-86CAEC84AC6A}">
-  <dimension ref="B1:M14"/>
+  <dimension ref="B2:N14"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="12.6640625" customWidth="1"/>
@@ -916,16 +952,11 @@
     <col min="7" max="7" width="7.08203125" customWidth="1"/>
     <col min="8" max="9" width="12.6640625" customWidth="1"/>
     <col min="10" max="11" width="8.6640625" customWidth="1"/>
-    <col min="12" max="12" width="12.6640625" customWidth="1"/>
-    <col min="13" max="13" width="41" customWidth="1"/>
+    <col min="12" max="13" width="12.6640625" customWidth="1"/>
+    <col min="14" max="14" width="41" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="G1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -938,29 +969,12 @@
       <c r="E2" s="4">
         <v>46162</v>
       </c>
-      <c r="G2" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L2" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="G2" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="14"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="5" t="s">
         <v>3</v>
       </c>
@@ -973,27 +987,32 @@
       <c r="E3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="3">
-        <v>1</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" s="6"/>
-      <c r="L3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="G3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="8" t="s">
         <v>7</v>
       </c>
@@ -1001,24 +1020,29 @@
       <c r="D4" s="9"/>
       <c r="E4" s="10"/>
       <c r="G4" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="M4" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="J4" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="M4" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="11" t="s">
         <v>22</v>
       </c>
@@ -1026,90 +1050,122 @@
       <c r="D5" s="12"/>
       <c r="E5" s="13"/>
       <c r="G5" s="3">
+        <v>2</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5" s="15"/>
+      <c r="N5" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="G6" s="3">
         <v>3</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="H6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="M6" s="15"/>
+      <c r="N6" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="G7" s="3">
+        <v>4</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="J7" s="15"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="G8" s="3">
+        <v>5</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="G6" s="3">
-        <v>4</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-    </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-    </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="J8" s="15"/>
+      <c r="K8" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -1117,9 +1173,10 @@
       <c r="K14" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B5:E5"/>
+    <mergeCell ref="G2:H2"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1128,7 +1185,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D2B5792-2F0E-414A-8E49-849F9596E6AF}">
-  <dimension ref="B1:M14"/>
+  <dimension ref="B2:N14"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="12.6640625" customWidth="1"/>
@@ -1137,16 +1194,11 @@
     <col min="7" max="7" width="7.08203125" customWidth="1"/>
     <col min="8" max="9" width="12.6640625" customWidth="1"/>
     <col min="10" max="11" width="8.6640625" customWidth="1"/>
-    <col min="12" max="12" width="12.6640625" customWidth="1"/>
-    <col min="13" max="13" width="41" customWidth="1"/>
+    <col min="12" max="13" width="12.6640625" customWidth="1"/>
+    <col min="14" max="14" width="41" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="G1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1159,29 +1211,12 @@
       <c r="E2" s="4">
         <v>46162</v>
       </c>
-      <c r="G2" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L2" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="G2" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="14"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="5" t="s">
         <v>3</v>
       </c>
@@ -1192,29 +1227,34 @@
         <v>5</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="3">
-        <v>1</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" s="6"/>
-      <c r="L3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+        <v>31</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="8" t="s">
         <v>7</v>
       </c>
@@ -1222,106 +1262,124 @@
       <c r="D4" s="9"/>
       <c r="E4" s="10"/>
       <c r="G4" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="J4" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="M4" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
       <c r="E5" s="13"/>
       <c r="G5" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-    </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5" s="15"/>
+      <c r="N5" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="G6" s="3">
+        <v>3</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="M6" s="15"/>
+      <c r="N6" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -1329,9 +1387,10 @@
       <c r="K14" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B5:E5"/>
+    <mergeCell ref="G2:H2"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
